--- a/artfynd/A 19874-2024 artfynd.xlsx
+++ b/artfynd/A 19874-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130861296</v>
+        <v>130861276</v>
       </c>
       <c r="B2" t="n">
-        <v>58564</v>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,7 +793,7 @@
         <v>130861272</v>
       </c>
       <c r="B3" t="n">
-        <v>58043</v>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130861276</v>
+        <v>130861296</v>
       </c>
       <c r="B4" t="n">
-        <v>58256</v>
+        <v>58636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,16 +916,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
